--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104604_W17.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104604_W17.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4895</v>
+        <v>2.7056</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8799</v>
+        <v>4.1679</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.3903</v>
+        <v>-1.4623</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0156</v>
+        <v>-0.0259</v>
       </c>
       <c r="H2" t="n">
-        <v>1.749</v>
+        <v>1.7409</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.7646</v>
+        <v>-1.7668</v>
       </c>
       <c r="J2" t="n">
-        <v>2.7396</v>
+        <v>2.7107</v>
       </c>
       <c r="K2" t="n">
-        <v>2.5211</v>
+        <v>2.5026</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2185</v>
+        <v>0.2081</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.7552</v>
+        <v>-2.7365</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7721</v>
+        <v>-0.7617</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.9831</v>
+        <v>-1.9749</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8247</v>
+        <v>1.0486</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5939</v>
+        <v>0.9125</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2308</v>
+        <v>0.1361</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0465</v>
+        <v>2.2115</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5931</v>
+        <v>3.9786</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.5466</v>
+        <v>-1.7671</v>
       </c>
       <c r="G3" t="n">
-        <v>5.2582</v>
+        <v>5.2391</v>
       </c>
       <c r="H3" t="n">
-        <v>1.244</v>
+        <v>1.2355</v>
       </c>
       <c r="I3" t="n">
-        <v>4.0142</v>
+        <v>4.0036</v>
       </c>
       <c r="J3" t="n">
-        <v>6.7525</v>
+        <v>6.715</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5038</v>
+        <v>2.4854</v>
       </c>
       <c r="L3" t="n">
-        <v>4.2487</v>
+        <v>4.2297</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.4944</v>
+        <v>-1.4759</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.2599</v>
+        <v>-1.2499</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6296</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2431</v>
+        <v>0.678</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3865</v>
+        <v>0.135</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="4">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.015</v>
+        <v>1.8724</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0416</v>
+        <v>2.9375</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0266</v>
+        <v>-1.0651</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2123</v>
+        <v>2.2206</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1327</v>
+        <v>1.1344</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0796</v>
+        <v>1.0862</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5153</v>
+        <v>2.5057</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7317</v>
+        <v>1.7237</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7837</v>
+        <v>0.782</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.303</v>
+        <v>-0.2851</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3756</v>
+        <v>0.2162</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5263</v>
+        <v>0.4319</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1506</v>
+        <v>-0.2157</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. APIC</t>
+          <t>M. ANDRIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.0564</v>
+        <v>-0.6469</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5344</v>
+        <v>1.0623</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.522</v>
+        <v>-1.7092</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8219</v>
+        <v>-0.8745000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.622</v>
+        <v>-1.0235</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1999</v>
+        <v>0.1489</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1612</v>
+        <v>1.7037</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0866</v>
+        <v>0.1551</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0746</v>
+        <v>1.5486</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9831</v>
+        <v>-2.5783</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7086</v>
+        <v>-1.1786</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2745</v>
+        <v>-1.3997</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7655</v>
+        <v>-0.6829</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4386</v>
+        <v>-0.4138</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3269</v>
+        <v>-0.2691</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. ANDRIC</t>
+          <t>F. ALONSO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.5274</v>
+        <v>-0.9489</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4656</v>
+        <v>0.4827</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.993</v>
+        <v>-1.4316</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8928</v>
+        <v>-5.1136</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0421</v>
+        <v>-1.5737</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1493</v>
+        <v>-3.5399</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7177</v>
+        <v>-1.3589</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1559</v>
+        <v>0.2511</v>
       </c>
       <c r="L6" t="n">
-        <v>1.5619</v>
+        <v>-1.61</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.6106</v>
+        <v>-3.7547</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.198</v>
+        <v>-1.8248</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.4126</v>
+        <v>-1.93</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9073</v>
+        <v>2.0487</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1342</v>
+        <v>2.0487</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5419</v>
+        <v>1.0265</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0253</v>
+        <v>0.7521</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5165999999999999</v>
+        <v>0.2744</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. ALONSO</t>
+          <t>D. APIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1069</v>
+        <v>-1.1743</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3871</v>
+        <v>-0.6339</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7197</v>
+        <v>-0.5405</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.0965</v>
+        <v>-0.8142</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5699</v>
+        <v>-0.6177</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.5266</v>
+        <v>-0.1965</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.3105</v>
+        <v>0.1607</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2731</v>
+        <v>0.0862</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.5835</v>
+        <v>0.0745</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.786</v>
+        <v>-0.9749</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.8429</v>
+        <v>-0.7039</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.9431</v>
+        <v>-0.271</v>
       </c>
       <c r="P7" t="n">
-        <v>2.0415</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0415</v>
+        <v>0.6829</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1446</v>
+        <v>0.6399</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1693</v>
+        <v>0.3436</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0248</v>
+        <v>0.2962</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0927</v>
+        <v>-0.5447</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. KURUCS</t>
+          <t>D. RUSSELL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.4531</v>
+        <v>-3.0077</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3026</v>
+        <v>0.0144</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.1505</v>
+        <v>-3.0221</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0496</v>
+        <v>-2.0819</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1845</v>
+        <v>0.7468</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2342</v>
+        <v>-2.8287</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5302</v>
+        <v>1.757</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3117</v>
+        <v>1.4372</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2185</v>
+        <v>0.3198</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5798</v>
+        <v>-3.8389</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1272</v>
+        <v>-0.6904</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.4526</v>
+        <v>-3.1485</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.6323</v>
+        <v>-0.4705</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8347</v>
+        <v>-0.3768</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7976</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ARANITOVIC</t>
+          <t>A. KURUCS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4715</v>
+        <v>-3.0456</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7115</v>
+        <v>-1.1315</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.76</v>
+        <v>-1.9141</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.9209</v>
+        <v>-1.0417</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.6854</v>
+        <v>0.1947</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.2355</v>
+        <v>-1.2365</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.6862</v>
+        <v>0.5183</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.551</v>
+        <v>0.3103</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.1352</v>
+        <v>0.2081</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.2347</v>
+        <v>-1.5601</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1344</v>
+        <v>-0.1155</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.1003</v>
+        <v>-1.4446</v>
       </c>
       <c r="P9" t="n">
-        <v>1.361</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R9" t="n">
-        <v>1.361</v>
+        <v>0.2276</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0042</v>
+        <v>-1.2299</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1179</v>
+        <v>-0.6483</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1137</v>
+        <v>-0.5816</v>
       </c>
       <c r="V9" t="n">
-        <v>1.0927</v>
+        <v>-0.7739</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0927</v>
+        <v>-0.7739</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. BRANKOVIC</t>
+          <t>A. ARANITOVIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6887</v>
+        <v>-3.0896</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5412</v>
+        <v>-1.1704</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.1476</v>
+        <v>-1.9192</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.8769</v>
+        <v>-5.9166</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.9422</v>
+        <v>-1.6832</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.9347</v>
+        <v>-4.2334</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.7972</v>
+        <v>-2.7078</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.2796</v>
+        <v>-0.5623</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4824</v>
+        <v>-2.1455</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.0797</v>
+        <v>-3.2087</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6626</v>
+        <v>-1.1209</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.4171</v>
+        <v>-2.0879</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S10" t="n">
-        <v>0.415</v>
+        <v>0.3717</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3902</v>
+        <v>0.448</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0248</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. RUSSELL</t>
+          <t>D. BRANKOVIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1832</v>
+        <v>-4.2215</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0336</v>
+        <v>-1.0379</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.1495</v>
+        <v>-3.1836</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0833</v>
+        <v>-5.8752</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7475000000000001</v>
+        <v>-2.9438</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.8308</v>
+        <v>-2.9314</v>
       </c>
       <c r="J11" t="n">
-        <v>1.7882</v>
+        <v>-1.8203</v>
       </c>
       <c r="K11" t="n">
-        <v>1.4577</v>
+        <v>-2.2967</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3304</v>
+        <v>0.4764</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.8715</v>
+        <v>-4.0549</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7103</v>
+        <v>-0.6471</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.1612</v>
+        <v>-3.4078</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6462</v>
+        <v>-0.1187</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.4608</v>
+        <v>-0.0795</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1854</v>
+        <v>-0.0392</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.34</v>
+        <v>-5.5324</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.4471</v>
+        <v>-4.5416</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8929</v>
+        <v>-0.9908</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.0759</v>
+        <v>-5.0865</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.5253</v>
+        <v>-1.5196</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.5506</v>
+        <v>-3.5669</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.9448</v>
+        <v>-2.9804</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6896</v>
+        <v>-0.7002</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.2552</v>
+        <v>-2.2802</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.1311</v>
+        <v>-2.1061</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8357</v>
+        <v>-0.8194</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.2954</v>
+        <v>-1.2866</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2311</v>
+        <v>0.058</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0998</v>
+        <v>-0.1467</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3309</v>
+        <v>0.2047</v>
       </c>
       <c r="V12" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-16.2762</v>
+        <v>-14.8774</v>
       </c>
       <c r="E13" t="n">
-        <v>3.022699999999999</v>
+        <v>4.128099999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-19.2987</v>
+        <v>-19.0056</v>
       </c>
       <c r="G13" t="n">
-        <v>-19.3629</v>
+        <v>-19.3704</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.3292</v>
+        <v>-4.309200000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-15.0338</v>
+        <v>-15.0614</v>
       </c>
       <c r="J13" t="n">
-        <v>7.466000000000002</v>
+        <v>7.2037</v>
       </c>
       <c r="K13" t="n">
-        <v>5.521400000000002</v>
+        <v>5.392399999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>1.9448</v>
+        <v>1.8115</v>
       </c>
       <c r="M13" t="n">
-        <v>-26.8291</v>
+        <v>-26.5741</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.8507</v>
+        <v>-9.701500000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-16.9785</v>
+        <v>-16.8727</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q13" t="n">
-        <v>-9.0733</v>
+        <v>-9.1052</v>
       </c>
       <c r="R13" t="n">
-        <v>11.3416</v>
+        <v>11.3816</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2722999999999992</v>
+        <v>1.6719</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4843000000000001</v>
+        <v>1.901</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2117999999999999</v>
+        <v>-0.2292000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5465</v>
+        <v>0.5448999999999995</v>
       </c>
       <c r="W13" t="n">
-        <v>4.1459</v>
+        <v>4.1288</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.5994</v>
+        <v>-3.5839</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.3621</v>
+        <v>6.483</v>
       </c>
       <c r="E14" t="n">
-        <v>5.8418</v>
+        <v>6.0173</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5202</v>
+        <v>0.4657</v>
       </c>
       <c r="G14" t="n">
-        <v>7.0041</v>
+        <v>6.9949</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2915</v>
+        <v>2.2865</v>
       </c>
       <c r="I14" t="n">
-        <v>4.7126</v>
+        <v>4.7085</v>
       </c>
       <c r="J14" t="n">
-        <v>8.682</v>
+        <v>8.6388</v>
       </c>
       <c r="K14" t="n">
-        <v>3.1272</v>
+        <v>3.1059</v>
       </c>
       <c r="L14" t="n">
-        <v>5.5548</v>
+        <v>5.533</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.6779</v>
+        <v>-1.6439</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8357</v>
+        <v>-0.8194</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8421999999999999</v>
+        <v>-0.8245</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0575</v>
+        <v>0.2968</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6103</v>
+        <v>0.5162</v>
       </c>
       <c r="V14" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W14" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.4818</v>
+        <v>4.4945</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2246</v>
+        <v>1.9004</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2572</v>
+        <v>2.5941</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0532</v>
+        <v>1.0451</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.245</v>
+        <v>-0.2632</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2982</v>
+        <v>1.3083</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2235</v>
+        <v>0.1958</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1496</v>
+        <v>-0.1766</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3732</v>
+        <v>0.3724</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8297</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0954</v>
+        <v>-0.0866</v>
       </c>
       <c r="O15" t="n">
-        <v>0.925</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>1.975</v>
+        <v>0.9941</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9084</v>
+        <v>0.6151</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0665</v>
+        <v>0.379</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2281</v>
+        <v>4.0057</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0033</v>
+        <v>3.9119</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2248</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7205</v>
+        <v>5.3844</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7534</v>
+        <v>0.9392</v>
       </c>
       <c r="I16" t="n">
-        <v>1.474</v>
+        <v>4.4452</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8762</v>
+        <v>6.0679</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2078</v>
+        <v>1.2271</v>
       </c>
       <c r="L16" t="n">
-        <v>1.6684</v>
+        <v>4.8408</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1557</v>
+        <v>-0.6835</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.2879</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1945</v>
+        <v>-0.3956</v>
       </c>
       <c r="P16" t="n">
-        <v>1.361</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1466</v>
+        <v>0.3937</v>
       </c>
       <c r="T16" t="n">
-        <v>0.127</v>
+        <v>0.1204</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0195</v>
+        <v>0.2733</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.7901</v>
+        <v>3.0508</v>
       </c>
       <c r="E17" t="n">
-        <v>3.2328</v>
+        <v>1.9815</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4427</v>
+        <v>1.0693</v>
       </c>
       <c r="G17" t="n">
-        <v>5.3802</v>
+        <v>0.7222</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9394</v>
+        <v>-0.7416</v>
       </c>
       <c r="I17" t="n">
-        <v>4.4408</v>
+        <v>1.4638</v>
       </c>
       <c r="J17" t="n">
-        <v>6.0909</v>
+        <v>1.8518</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2397</v>
+        <v>0.2068</v>
       </c>
       <c r="L17" t="n">
-        <v>4.8512</v>
+        <v>1.645</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7107</v>
+        <v>-1.1296</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3003</v>
+        <v>-0.9485</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4104</v>
+        <v>-0.1811</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8169</v>
+        <v>0.9628</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5898</v>
+        <v>0.1297</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2271</v>
+        <v>0.8331</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4813</v>
+        <v>1.0892</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3113</v>
+        <v>2.294</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7926</v>
+        <v>-1.2048</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.1538</v>
+        <v>1.7129</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.9219</v>
+        <v>1.9389</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2319</v>
+        <v>-0.226</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.8557</v>
+        <v>2.5266</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.701</v>
+        <v>2.5715</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1547</v>
+        <v>-0.0449</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2981</v>
+        <v>-0.8138</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2209</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0772</v>
+        <v>-0.1811</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1342</v>
+        <v>0.2276</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>0.2276</v>
       </c>
       <c r="S18" t="n">
-        <v>1.7297</v>
+        <v>-1.0091</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5444</v>
+        <v>-0.3904</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1853</v>
+        <v>-0.6187</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7712</v>
+        <v>0.1578</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X18" t="n">
-        <v>0.7712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7383999999999999</v>
+        <v>1.0846</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7591</v>
+        <v>-1.4488</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0206</v>
+        <v>2.5333</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5338000000000001</v>
+        <v>-2.162</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5817</v>
+        <v>-1.9296</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0479</v>
+        <v>-0.2324</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8867</v>
+        <v>-1.8782</v>
       </c>
       <c r="K19" t="n">
-        <v>1.7001</v>
+        <v>-1.7139</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1866</v>
+        <v>-0.1643</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.353</v>
+        <v>-0.2838</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1185</v>
+        <v>-0.2157</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2345</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1781</v>
+        <v>1.3345</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2994</v>
+        <v>0.4294</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1213</v>
+        <v>0.905</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7071</v>
+        <v>0.7739</v>
       </c>
       <c r="W19" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6048</v>
+        <v>0.6435999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0851</v>
+        <v>1.6123</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4802</v>
+        <v>-0.9687</v>
       </c>
       <c r="G20" t="n">
-        <v>1.7092</v>
+        <v>0.5322</v>
       </c>
       <c r="H20" t="n">
-        <v>1.9437</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2345</v>
+        <v>-0.0399</v>
       </c>
       <c r="J20" t="n">
-        <v>2.5504</v>
+        <v>1.8647</v>
       </c>
       <c r="K20" t="n">
-        <v>2.5904</v>
+        <v>1.6785</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.04</v>
+        <v>0.1862</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8411</v>
+        <v>-1.3325</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-1.1064</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1945</v>
+        <v>-0.226</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2268</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.492</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6261</v>
+        <v>0.1833</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8659</v>
+        <v>-0.0915</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1607</v>
+        <v>0.7025</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1607</v>
+        <v>0.7025</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. LYLES</t>
+          <t>E. AMOSOV</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5750999999999999</v>
+        <v>0.1605</v>
       </c>
       <c r="E21" t="n">
-        <v>1.9483</v>
+        <v>-0.0352</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3732</v>
+        <v>0.1958</v>
       </c>
       <c r="G21" t="n">
-        <v>3.6492</v>
+        <v>0.3359</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3808</v>
+        <v>0.02</v>
       </c>
       <c r="I21" t="n">
-        <v>2.2684</v>
+        <v>0.3159</v>
       </c>
       <c r="J21" t="n">
-        <v>3.9868</v>
+        <v>0.0345</v>
       </c>
       <c r="K21" t="n">
-        <v>1.5239</v>
+        <v>0.0345</v>
       </c>
       <c r="L21" t="n">
-        <v>2.4629</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3375</v>
+        <v>0.3014</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1431</v>
+        <v>-0.0144</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1945</v>
+        <v>0.3159</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.8147</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3796</v>
+        <v>-0.1754</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2299</v>
+        <v>-0.0697</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1497</v>
+        <v>-0.1057</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. AMOSOV</t>
+          <t>T. LYLES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1273</v>
+        <v>-0.1203</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0349</v>
+        <v>1.6933</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1622</v>
+        <v>-1.8136</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3333</v>
+        <v>3.6634</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0187</v>
+        <v>1.3869</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3145</v>
+        <v>2.2765</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0346</v>
+        <v>3.9745</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0346</v>
+        <v>1.5168</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.4576</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2986</v>
+        <v>-0.3111</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0159</v>
+        <v>-0.13</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3145</v>
+        <v>-0.1811</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.206</v>
+        <v>-0.3284</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0696</v>
+        <v>-0.0049</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1364</v>
+        <v>-0.3235</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="23">
@@ -2203,40 +2203,40 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.3675</v>
+        <v>-1.1115</v>
       </c>
       <c r="E23" t="n">
-        <v>1.4188</v>
+        <v>1.4104</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.7863</v>
+        <v>-2.5219</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7271</v>
+        <v>0.7316</v>
       </c>
       <c r="H23" t="n">
-        <v>1.8066</v>
+        <v>1.8038</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="J23" t="n">
-        <v>1.697</v>
+        <v>1.6892</v>
       </c>
       <c r="K23" t="n">
-        <v>1.697</v>
+        <v>1.6892</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9699</v>
+        <v>-0.9576</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1096</v>
+        <v>0.1146</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2248,22 +2248,22 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.002</v>
+        <v>-0.7537</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2782</v>
+        <v>-0.2788</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7238</v>
+        <v>-0.4749</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.6415</v>
+        <v>-1.301</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.3019</v>
+        <v>-0.2001</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3396</v>
+        <v>-1.1009</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3697</v>
+        <v>0.3725</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.899</v>
+        <v>-0.8935</v>
       </c>
       <c r="I24" t="n">
-        <v>1.2688</v>
+        <v>1.2661</v>
       </c>
       <c r="J24" t="n">
-        <v>0.185</v>
+        <v>0.1694</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.6345</v>
       </c>
       <c r="L24" t="n">
-        <v>0.8156</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1847</v>
+        <v>0.2032</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2685</v>
+        <v>-0.259</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1454</v>
+        <v>-0.8117</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4869</v>
+        <v>-0.3695</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6584</v>
+        <v>-0.4422</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,58 +2359,58 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.104</v>
+        <v>-1.4178</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.5669</v>
+        <v>-0.1314</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.5371</v>
+        <v>-1.2864</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0364</v>
+        <v>0.0373</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.8139</v>
+        <v>-0.8101</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8502999999999999</v>
+        <v>0.8475</v>
       </c>
       <c r="J25" t="n">
-        <v>1.4716</v>
+        <v>1.4392</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2109</v>
+        <v>0.1961</v>
       </c>
       <c r="L25" t="n">
-        <v>1.2607</v>
+        <v>1.243</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.4352</v>
+        <v>-1.4018</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.0248</v>
+        <v>-1.0062</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.4104</v>
+        <v>-0.3956</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R25" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.6867</v>
+        <v>-0.9998</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9043</v>
+        <v>-0.4324</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7824</v>
+        <v>-0.5675</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>16.276</v>
+        <v>17.0613</v>
       </c>
       <c r="E26" t="n">
-        <v>19.2988</v>
+        <v>19.0056</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.022699999999999</v>
+        <v>-1.9443</v>
       </c>
       <c r="G26" t="n">
-        <v>19.3629</v>
+        <v>19.3704</v>
       </c>
       <c r="H26" t="n">
-        <v>4.329199999999999</v>
+        <v>4.3094</v>
       </c>
       <c r="I26" t="n">
-        <v>15.0338</v>
+        <v>15.0613</v>
       </c>
       <c r="J26" t="n">
-        <v>26.829</v>
+        <v>26.5742</v>
       </c>
       <c r="K26" t="n">
-        <v>9.8505</v>
+        <v>9.7014</v>
       </c>
       <c r="L26" t="n">
-        <v>16.9787</v>
+        <v>16.8727</v>
       </c>
       <c r="M26" t="n">
-        <v>-7.466099999999999</v>
+        <v>-7.2037</v>
       </c>
       <c r="N26" t="n">
-        <v>-5.5214</v>
+        <v>-5.392099999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.945</v>
+        <v>-1.8112</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.2684</v>
+        <v>-2.2764</v>
       </c>
       <c r="Q26" t="n">
-        <v>-11.3417</v>
+        <v>-11.3816</v>
       </c>
       <c r="R26" t="n">
-        <v>9.073300000000001</v>
+        <v>9.105300000000002</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2722000000000002</v>
+        <v>0.5117999999999996</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2117000000000006</v>
+        <v>0.2290000000000002</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.4839999999999999</v>
+        <v>0.2826000000000001</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.5464</v>
+        <v>-0.5448000000000002</v>
       </c>
       <c r="W26" t="n">
-        <v>3.5995</v>
+        <v>3.584</v>
       </c>
       <c r="X26" t="n">
-        <v>-4.1459</v>
+        <v>-4.1288</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104604_W17.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104604_W17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104604_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104604_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104604_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104604_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104604_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104604_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104604_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104604_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104604_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104604_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104604_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-3.5839</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104604_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104604_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104604_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104604_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104604_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104604_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104604_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104604_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104604_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104604_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104604_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104604_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-4.1288</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
